--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/PLANAbPiaSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8EABB3-40FE-5144-817D-3C4CE99B98D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16E712-EE45-DC41-B1E1-B54F7EFDB768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
   <si>
     <t>PLANAbPiaSY Potential Land Area Newly Affected by Policy in a Single Year</t>
   </si>
@@ -660,7 +660,13 @@
       <sheetData sheetId="16"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
+      <sheetData sheetId="19">
+        <row r="4">
+          <cell r="A4">
+            <v>3.6666666666666665</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3414,13 +3420,7 @@
         <f>J3*J4</f>
         <v>1606150</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N5">
-        <f>N3/N4</f>
-        <v>0</v>
-      </c>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>

--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/PLANAbPiaSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F16E712-EE45-DC41-B1E1-B54F7EFDB768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DA043D-FCA6-2D4C-9C12-24A6DEA6E73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="120">
   <si>
     <t>PLANAbPiaSY Potential Land Area Newly Affected by Policy in a Single Year</t>
   </si>
@@ -347,13 +347,76 @@
   </si>
   <si>
     <t>Length of sumulation</t>
+  </si>
+  <si>
+    <t>Despite their considerable environmental significance, only 6 % of Indonesian peatlands remain intact while 13.4–14.9 million ha (87–97 %) are considered degraded</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2212041624001001?ref=pdf_download&amp;fr=RR-2&amp;rr=967b26ebdf079032</t>
+  </si>
+  <si>
+    <t>Nevertheless, degraded and drained peatlands are estimated to emit 1.9 gigatonnes of CO2e annually</t>
+  </si>
+  <si>
+    <t>https://www.nature.org/en-us/about-us/where-we-work/asia-pacific/indonesia/stories-in-indonesia/peatland-conservation/</t>
+  </si>
+  <si>
+    <t>Indonesia’s peatlands have not been fully and accurately mapped, so estimates of their extent vary widely, ranging from the official figure of approximately 15 million hectares (ha) to more than 22 million ha.2,</t>
+  </si>
+  <si>
+    <t>https://gggi.org/wp-content/uploads/2020/11/Indonesia-Peat-Insight-Brief_October2020_tentative.pdf</t>
+  </si>
+  <si>
+    <t>Emissions from degradated land (Gt CO2e/year)</t>
+  </si>
+  <si>
+    <t>Millions acres</t>
+  </si>
+  <si>
+    <t>Millions ha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peatland area </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Degradated land </t>
+  </si>
+  <si>
+    <t>Acres</t>
+  </si>
+  <si>
+    <t>Conversely, rewetting 590 km2/year aligns with Indonesia’s FOLU Net Sink 2030 target (−140 Mt CO2e) and mitigates 1.4–1.6 MtCO2 annually</t>
+  </si>
+  <si>
+    <t>https://www.mdpi.com/3042-4658/2/3/17</t>
+  </si>
+  <si>
+    <t>2030 target millions ha</t>
+  </si>
+  <si>
+    <t>2030 target acres</t>
+  </si>
+  <si>
+    <t>Peatland Sequestration Rate (Mg C/ha/year)</t>
+  </si>
+  <si>
+    <t>0.5 to 1.5</t>
+  </si>
+  <si>
+    <t>Mg C to t CO2</t>
+  </si>
+  <si>
+    <t>Peatland Sequestration Rate (t CO₂/ha/year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 t CO2 per ha </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,14 +507,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1A1A1A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -509,7 +582,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -537,27 +610,31 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -612,6 +689,56 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2082800</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>178982</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{052BB98B-A4C3-C2D9-A0CB-692D389FBC80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8851900"/>
+          <a:ext cx="7772400" cy="3417482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -907,7 +1034,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="19" t="s">
         <v>5</v>
       </c>
     </row>
@@ -962,7 +1089,7 @@
       </c>
     </row>
     <row r="21" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="19" t="s">
         <v>15</v>
       </c>
     </row>
@@ -996,7 +1123,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="19" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3180,107 +3307,107 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="22"/>
+      <c r="B1" s="23" t="s">
         <v>90</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="23" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="22">
         <v>0</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="20">
         <v>1000000</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2">
         <f>B2/$D$2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="24">
         <v>7921902</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3">
         <f t="shared" ref="G3:G7" si="0">B3/$D$2</f>
         <v>7.9219020000000002</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="22">
         <v>0</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="24">
         <v>7921902</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>7.9219020000000002</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="24">
         <v>7253293</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>7.2532930000000002</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="24">
         <v>3712996</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>3.712996</v>
       </c>
@@ -3292,7 +3419,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N998"/>
+  <dimension ref="A1:P1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
@@ -3307,37 +3434,37 @@
     <col min="15" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="E1" s="19" t="s">
+      <c r="B1" s="31"/>
+      <c r="E1" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="20"/>
+      <c r="F1" s="31"/>
       <c r="G1" s="13"/>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="20"/>
-      <c r="M1" s="19" t="s">
+      <c r="J1" s="31"/>
+      <c r="M1" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="20"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N1" s="31"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="25">
         <f>'CO2 Sequestrated'!G3</f>
         <v>7.9219020000000002</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="21" t="s">
         <v>86</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -3349,12 +3476,12 @@
       <c r="M2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="N2" s="29">
+      <c r="N2" s="25">
         <f>'CO2 Sequestrated'!G6</f>
         <v>7.2532930000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="E3" s="1" t="s">
@@ -3373,7 +3500,7 @@
       <c r="M3" s="1"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -3399,7 +3526,7 @@
         <v>2.4710538146999999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
@@ -3422,7 +3549,7 @@
       </c>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="15"/>
       <c r="E6" s="1" t="s">
@@ -3438,8 +3565,14 @@
       <c r="N6" s="2">
         <v>363.85</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6">
+        <v>1.5</v>
+      </c>
+      <c r="P6" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="15"/>
       <c r="E7" s="2" t="s">
@@ -3456,7 +3589,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
@@ -3480,8 +3613,16 @@
         <f>N6*N7</f>
         <v>363850000</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="17">
+        <f>O6*N7</f>
+        <v>1500000</v>
+      </c>
+      <c r="P8" s="17">
+        <f>P6*N7</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>93</v>
       </c>
@@ -3502,26 +3643,56 @@
         <v>96</v>
       </c>
       <c r="N9" s="15">
-        <f>N8/N2</f>
-        <v>50163422.324177444</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+        <f>(N8/N2)*N4</f>
+        <v>123956516.0925658</v>
+      </c>
+      <c r="O9" s="20">
+        <f>(O8/N2)*N4</f>
+        <v>511020.40439425234</v>
+      </c>
+      <c r="P9" s="20">
+        <f>(P8*N13)/N4</f>
+        <v>2967964.5001541134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="P11" s="20"/>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="N12" s="2">
+        <v>3.6669999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="20"/>
+      <c r="B13" s="31"/>
       <c r="E13" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M13" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="N13" s="2">
+        <f>((0.5+1.5)/2)*N12</f>
+        <v>3.6669999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="25">
         <f>'CO2 Sequestrated'!G7</f>
         <v>3.712996</v>
       </c>
@@ -3531,10 +3702,15 @@
       <c r="F14" s="17">
         <v>50100000</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="17">
+        <f>(O8/N13)*N4</f>
+        <v>1010793.7611262612</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="E15" s="18" t="s">
@@ -3543,14 +3719,14 @@
       <c r="M15" s="2"/>
       <c r="N15" s="15"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B16">
         <v>2.4710538146999999</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="27" t="s">
         <v>98</v>
       </c>
       <c r="F16">
@@ -3567,10 +3743,10 @@
         <f>B15/B16</f>
         <v>0</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="20">
         <f>F14/F16</f>
         <v>1002000</v>
       </c>
@@ -3597,7 +3773,7 @@
       <c r="A20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="20">
         <f>B18*B19</f>
         <v>21560000</v>
       </c>
@@ -3627,10 +3803,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B26" s="30"/>
+      <c r="B26" s="26"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
@@ -3640,24 +3816,28 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="22"/>
+      <c r="B28" s="20"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="22"/>
+      <c r="B29" s="20"/>
       <c r="E29" s="2"/>
       <c r="F29" s="15"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
+      <c r="A30" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="E30" s="2"/>
       <c r="F30" s="15"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="22"/>
+      <c r="A31" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="20"/>
       <c r="E31" s="1"/>
       <c r="F31" s="15"/>
     </row>
@@ -3665,54 +3845,145 @@
       <c r="E32" s="1"/>
       <c r="F32" s="15"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40">
+        <v>22</v>
+      </c>
+      <c r="C40">
+        <f>N4*B40</f>
+        <v>54.363183923399994</v>
+      </c>
+      <c r="D40" s="20">
+        <f>C40*1000000</f>
+        <v>54363183.923399992</v>
+      </c>
+      <c r="E40" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="F40" s="20">
+        <f>E40*N4*1000000</f>
+        <v>4200791.4849899998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41">
+        <f>(13.4+14.9)/2</f>
+        <v>14.15</v>
+      </c>
+      <c r="C41">
+        <f>N4*B41</f>
+        <v>34.965411478005002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B43">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F47" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4631,6 +4902,12 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
@@ -4641,10 +4918,14 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E15" r:id="rId1" location=":~:text=Out%20of%20Indonesia's%2027%20million,among%20environmental%20groups%20and%20lawmakers." xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="A31" r:id="rId2" xr:uid="{D2C2543B-2FE3-2741-AA39-42D63CDCE2A3}"/>
+    <hyperlink ref="A34" r:id="rId3" xr:uid="{F4A67961-5D19-5B44-A132-82205BEA5C53}"/>
+    <hyperlink ref="A64" r:id="rId4" xr:uid="{C8FA7D2F-09A8-C24D-B8CD-0ACDAE7CCE6C}"/>
+    <hyperlink ref="A68" r:id="rId5" xr:uid="{2BF5590A-7311-964A-9A14-7F654CC6792A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -5455,7 +5736,7 @@
         <v>1606150</v>
       </c>
       <c r="C5" s="15">
-        <f t="shared" ref="C5:AZ5" si="3">B5</f>
+        <f t="shared" ref="C5:AZ6" si="3">B5</f>
         <v>1606150</v>
       </c>
       <c r="D5" s="15">
@@ -5660,208 +5941,206 @@
         <v>83</v>
       </c>
       <c r="B6" s="15">
-        <f>'Potential land area'!N9</f>
-        <v>50163422.324177444</v>
+        <v>0</v>
       </c>
       <c r="C6" s="15">
-        <f t="shared" ref="C6:AZ6" si="4">B6</f>
-        <v>50163422.324177444</v>
+        <f>B6</f>
+        <v>0</v>
       </c>
       <c r="D6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="E6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="F6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="G6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="H6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f>'Potential land area'!P9</f>
+        <v>2967964.5001541134</v>
       </c>
       <c r="J6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="K6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="L6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="M6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="N6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="O6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="P6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="Q6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="R6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="S6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="T6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>2967964.5001541134</v>
       </c>
       <c r="U6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <v>0</v>
       </c>
       <c r="V6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="W6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="X6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Y6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="Z6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AA6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AB6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AC6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AD6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AE6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AF6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AG6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AH6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AI6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AJ6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AK6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AL6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AM6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AN6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AO6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AP6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AQ6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AR6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AS6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AT6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AU6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AV6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AW6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AX6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AY6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AZ6" s="15">
-        <f t="shared" si="4"/>
-        <v>50163422.324177444</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.2">
@@ -5873,205 +6152,210 @@
         <v>5806631.6257814448</v>
       </c>
       <c r="C7" s="15">
-        <f t="shared" ref="C7:AZ7" si="5">B7</f>
+        <f t="shared" ref="C7:AZ7" si="4">B7</f>
         <v>5806631.6257814448</v>
       </c>
       <c r="D7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="E7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="F7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="G7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="H7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="L7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="M7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="N7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="O7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="P7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="Q7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="R7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="S7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="T7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="U7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="V7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="W7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="X7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="Y7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="Z7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AA7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AB7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AC7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AD7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AE7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AF7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AG7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AH7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AI7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AJ7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AK7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AL7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AM7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AN7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AO7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AP7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AQ7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AR7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AS7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AT7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AU7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AV7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AW7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AX7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AY7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
       <c r="AZ7" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>5806631.6257814448</v>
       </c>
+    </row>
+    <row r="10" spans="1:52" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7056,5 +7340,8 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <ignoredErrors>
+    <ignoredError sqref="I6" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/PLANAbPiaSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DA043D-FCA6-2D4C-9C12-24A6DEA6E73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF033EB-207D-1E4D-AD87-DE79FF73337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -627,14 +627,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3435,23 +3435,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="E1" s="30" t="s">
+      <c r="B1" s="33"/>
+      <c r="E1" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="31"/>
+      <c r="F1" s="33"/>
       <c r="G1" s="13"/>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="31"/>
-      <c r="M1" s="30" t="s">
+      <c r="J1" s="33"/>
+      <c r="M1" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="31"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3568,7 +3568,7 @@
       <c r="O6">
         <v>1.5</v>
       </c>
-      <c r="P6" s="33">
+      <c r="P6" s="31">
         <v>2</v>
       </c>
     </row>
@@ -3673,10 +3673,10 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="31"/>
+      <c r="B13" s="33"/>
       <c r="E13" s="16" t="s">
         <v>73</v>
       </c>
@@ -3899,7 +3899,7 @@
         <f>C40*1000000</f>
         <v>54363183.923399992</v>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="30">
         <v>1.7</v>
       </c>
       <c r="F40" s="20">
@@ -3918,6 +3918,10 @@
       <c r="C41">
         <f>N4*B41</f>
         <v>34.965411478005002</v>
+      </c>
+      <c r="D41" s="20">
+        <f>C41*1000000</f>
+        <v>34965411.478004999</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
+++ b/InputData/land/PLANAbPiaSY/Potential Land Area Newly Affected by Pol in a Single Yr.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/land/PLANAbPiaSY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tfranc03/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF033EB-207D-1E4D-AD87-DE79FF73337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D658B9EC-9C84-8542-B3C2-F5EF64FA274F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="28300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Set Asides" sheetId="2" r:id="rId2"/>
     <sheet name="CO2 Sequestrated" sheetId="5" r:id="rId3"/>
     <sheet name="Potential land area" sheetId="3" r:id="rId4"/>
-    <sheet name="PLANAbPiaSY" sheetId="4" r:id="rId5"/>
+    <sheet name="Scratchpad" sheetId="6" r:id="rId5"/>
+    <sheet name="PLANAbPiaSY" sheetId="4" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="acres_per_hectare">#REF!</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="131">
   <si>
     <t>PLANAbPiaSY Potential Land Area Newly Affected by Policy in a Single Year</t>
   </si>
@@ -410,6 +411,39 @@
   </si>
   <si>
     <t xml:space="preserve">60 t CO2 per ha </t>
+  </si>
+  <si>
+    <t>Sums of the PLANAbPiaSY tab (for new structure)</t>
+  </si>
+  <si>
+    <t>Implied from 31 July PLAN file</t>
+  </si>
+  <si>
+    <t>Acres (since summed)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Emissions aren't significant; another way to say "avoid defo"?</t>
+  </si>
+  <si>
+    <t>griscom</t>
+  </si>
+  <si>
+    <t>Griscom for Rice (WRONG)</t>
+  </si>
+  <si>
+    <t>Griscom: Reforestation</t>
+  </si>
+  <si>
+    <t>Griscom: Natural forest management</t>
+  </si>
+  <si>
+    <t>Griscom: Peatland Restoration</t>
+  </si>
+  <si>
+    <t>Values from Potential Land Area calcs</t>
   </si>
 </sst>
 </file>
@@ -582,7 +616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -631,10 +665,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -657,10 +699,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>174625</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4048125" cy="4448175"/>
     <xdr:pic>
@@ -681,6 +723,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12534900" y="1393825"/>
+          <a:ext cx="4048125" cy="4448175"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -698,7 +744,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>2082800</xdr:colOff>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>178982</xdr:rowOff>
     </xdr:to>
@@ -731,6 +777,99 @@
         <a:xfrm>
           <a:off x="0" y="8851900"/>
           <a:ext cx="7772400" cy="3417482"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>97459</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB70F79-FCCD-4083-385D-7BF2BCDA119A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16408400" y="8331200"/>
+          <a:ext cx="7772400" cy="1951659"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>59032</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D2B5D95-026A-294D-5F67-9662CF4C2B74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="584200" y="3022600"/>
+          <a:ext cx="7772400" cy="5634332"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3423,35 +3562,36 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="39.33203125" customWidth="1"/>
-    <col min="2" max="3" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="40.33203125" customWidth="1"/>
     <col min="6" max="8" width="10.6640625" customWidth="1"/>
     <col min="9" max="9" width="43.1640625" customWidth="1"/>
     <col min="10" max="12" width="10.6640625" customWidth="1"/>
     <col min="13" max="13" width="35.1640625" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" customWidth="1"/>
+    <col min="14" max="14" width="18.1640625" customWidth="1"/>
     <col min="15" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="E1" s="32" t="s">
+      <c r="B1" s="35"/>
+      <c r="E1" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="33"/>
+      <c r="F1" s="35"/>
       <c r="G1" s="13"/>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="M1" s="32" t="s">
+      <c r="J1" s="35"/>
+      <c r="M1" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="33"/>
+      <c r="N1" s="35"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3507,6 +3647,9 @@
       <c r="B4" s="2">
         <v>212.02</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>70</v>
       </c>
@@ -3642,7 +3785,7 @@
       <c r="M9" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="33">
         <f>(N8/N2)*N4</f>
         <v>123956516.0925658</v>
       </c>
@@ -3673,10 +3816,10 @@
       </c>
     </row>
     <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="33"/>
+      <c r="B13" s="35"/>
       <c r="E13" s="16" t="s">
         <v>73</v>
       </c>
@@ -3758,6 +3901,9 @@
       <c r="B18" s="2">
         <v>21.56</v>
       </c>
+      <c r="C18" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
@@ -3918,10 +4064,6 @@
       <c r="C41">
         <f>N4*B41</f>
         <v>34.965411478005002</v>
-      </c>
-      <c r="D41" s="20">
-        <f>C41*1000000</f>
-        <v>34965411.478004999</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4934,6 +5076,116 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DA1CAE4-3810-2440-B0A3-9A0D32C200D9}">
+  <dimension ref="A4:D47"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="37" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="32">
+        <f>SUM(PLANAbPiaSY!B2:AZ2)</f>
+        <v>51102000</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="32">
+        <f>SUM(PLANAbPiaSY!B3:AZ3)</f>
+        <v>1364952507.6174879</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="32">
+        <f>SUM(PLANAbPiaSY!B4:AZ4)</f>
+        <v>232492080.46237782</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="32">
+        <f>SUM(PLANAbPiaSY!B5:AZ5)</f>
+        <v>81913650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="32">
+        <f>SUM(PLANAbPiaSY!B6:AZ6)</f>
+        <v>35615574.001849368</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="32">
+        <f>SUM(PLANAbPiaSY!B7:AZ7)</f>
+        <v>296138212.91485363</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B47" s="32"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F497D"/>
